--- a/output/pdf_financials_xlsx/GPAC.xlsx
+++ b/output/pdf_financials_xlsx/GPAC.xlsx
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.06854499999999999</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.268069</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.516686</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.266441</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.223393</v>
       </c>
     </row>
     <row r="13">
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-12.10282</v>
+        <v>-12.171365</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.071322</v>
+        <v>-6.339391</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.411668</v>
+        <v>-4.928354</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-18.167354</v>
+        <v>-18.433795</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-4.061836</v>
+        <v>-4.285229</v>
       </c>
     </row>
     <row r="28">
@@ -1063,19 +1063,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-11.930342</v>
+        <v>-11.998887</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.963143</v>
+        <v>-6.231212</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.317323</v>
+        <v>-4.834009</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-18.103709</v>
+        <v>-18.37015</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-4.020094</v>
+        <v>-4.243487</v>
       </c>
     </row>
     <row r="30">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">

--- a/output/pdf_financials_xlsx/GPAC.xlsx
+++ b/output/pdf_financials_xlsx/GPAC.xlsx
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1.107952</v>
+        <v>1.334625</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.59784</v>
+        <v>0.836288</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.893855</v>
+        <v>1.36892</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.300823</v>
+        <v>1.818195</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.906108</v>
+        <v>2.763033</v>
       </c>
     </row>
     <row r="8">
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.107952</v>
+        <v>1.334625</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.59784</v>
+        <v>0.836288</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.893855</v>
+        <v>1.36892</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.300823</v>
+        <v>1.818195</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.906108</v>
+        <v>2.763033</v>
       </c>
     </row>
     <row r="11">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-1.107952</v>
+        <v>-1.334625</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-6.339391</v>
@@ -2879,16 +2879,16 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.017897</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.007078</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.003273</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.011761</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -2913,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.094862</v>
       </c>
     </row>
     <row r="112">
@@ -3001,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.93869</v>
       </c>
     </row>
     <row r="116">
@@ -3429,7 +3429,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.094862</v>
       </c>
     </row>
     <row r="135">
@@ -3451,7 +3451,7 @@
         <v>-8.187611</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-14.997227</v>
+        <v>-15.092089</v>
       </c>
     </row>
   </sheetData>
@@ -6034,7 +6034,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="n">
         <v>0.017897</v>
       </c>
@@ -6988,7 +6992,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -7105,7 +7113,11 @@
           <t>Purchases of equipment</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -7220,7 +7232,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -8549,7 +8565,11 @@
           <t>Directors’ fees (Note 16)</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -8822,7 +8842,11 @@
           <t>Office expenses (Note 16)</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -10010,7 +10034,11 @@
           <t>Directors’ fees (Note 15)</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -10172,7 +10200,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E167" s="5" t="n">
         <v>0.154673</v>
       </c>
@@ -10742,7 +10774,11 @@
           <t>Directors’ fees (Note 14)</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -11156,7 +11192,11 @@
           <t>Directors’ fees (Note 13)</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E191" s="5" t="n">
         <v>0.07199999999999999</v>
       </c>
